--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00687B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00687B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13EF19D1-2D28-41F1-86D9-636B5A0B1FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F648E7C8-421A-44DA-9672-BB5DE43755C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{8E51E4BC-9948-4B04-866E-437C6A4BA30F}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{D2944EC8-81FF-46B8-9D02-8263C111FDBC}"/>
   </bookViews>
   <sheets>
     <sheet name="00687B-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1598,20 +1598,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE497154-17AE-4E14-B66C-E20B134CEC17}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF24FA29-EA68-4408-8B22-A9F97E82DCAB}">
   <dimension ref="A1:R47"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1639,7 +1639,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1669,7 +1669,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1765,7 +1765,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>4.37</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2023</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2022</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>25</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2021</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>25</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2020</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>25</v>
       </c>
@@ -3321,7 +3321,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>25</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>25</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>2019</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>25</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>25</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>25</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2018</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
         <v>25</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="s">
         <v>25</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
         <v>25</v>
       </c>
@@ -3933,7 +3933,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
         <v>25</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>2017</v>
       </c>
@@ -4043,7 +4043,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>25</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="39" t="s">
         <v>85</v>
       </c>
